--- a/프로젝트 보고/프로젝트관리 간트차트.xlsx
+++ b/프로젝트 보고/프로젝트관리 간트차트.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project1\프로젝트 보고\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D407E685-EBB0-49F2-9C2F-C959CDEAA2AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA443724-47DE-448C-82A0-81C354C135B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -118,19 +118,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>시계열 분석</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>모델링</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Random Forest 모델링</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>XGBoost 모델링</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -189,6 +177,18 @@
   </si>
   <si>
     <t>실시간 연동 시스템 구현</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Random Forest/XGBoost 모델링</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Transform/LSTM+CNN 모델링</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시계열 분석/데이터 전처리</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -444,7 +444,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -481,13 +481,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -496,22 +496,22 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -520,32 +520,23 @@
     <xf numFmtId="0" fontId="7" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -553,63 +544,75 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -620,21 +623,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -999,94 +987,91 @@
     <col min="13" max="13" width="6.296875" style="1" customWidth="1"/>
     <col min="14" max="14" width="5.69921875" style="1" customWidth="1"/>
     <col min="15" max="15" width="6.09765625" style="1" customWidth="1"/>
-    <col min="16" max="18" width="5.69921875" style="33" customWidth="1"/>
+    <col min="16" max="18" width="5.69921875" style="1" customWidth="1"/>
     <col min="19" max="16384" width="2.19921875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" s="2" customFormat="1">
-      <c r="A1" s="25"/>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="53"/>
-      <c r="M1" s="53"/>
-      <c r="N1" s="53"/>
-      <c r="O1" s="53"/>
-      <c r="P1" s="53"/>
-      <c r="Q1" s="53"/>
-      <c r="R1" s="53"/>
-      <c r="S1" s="61"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="42"/>
+      <c r="L1" s="42"/>
+      <c r="M1" s="42"/>
+      <c r="N1" s="42"/>
+      <c r="O1" s="42"/>
+      <c r="P1" s="42"/>
+      <c r="Q1" s="42"/>
+      <c r="R1" s="42"/>
+      <c r="S1" s="44"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" customHeight="1">
       <c r="A2" s="2"/>
-      <c r="B2" s="62" t="s">
-        <v>30</v>
-      </c>
-      <c r="C2" s="63"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="49"/>
-      <c r="L2" s="49"/>
-      <c r="M2" s="49"/>
-      <c r="N2" s="49"/>
-      <c r="O2" s="49"/>
-      <c r="P2" s="49"/>
-      <c r="Q2" s="49"/>
-      <c r="R2" s="55"/>
+      <c r="B2" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
+      <c r="P2" s="55"/>
+      <c r="Q2" s="55"/>
+      <c r="R2" s="56"/>
       <c r="S2" s="3"/>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="2"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="57"/>
-      <c r="L3" s="57"/>
-      <c r="M3" s="57"/>
-      <c r="N3" s="57"/>
-      <c r="O3" s="57"/>
-      <c r="P3" s="57"/>
-      <c r="Q3" s="57"/>
-      <c r="R3" s="58"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="58"/>
+      <c r="L3" s="58"/>
+      <c r="M3" s="58"/>
+      <c r="N3" s="58"/>
+      <c r="O3" s="58"/>
+      <c r="P3" s="58"/>
+      <c r="Q3" s="58"/>
+      <c r="R3" s="59"/>
       <c r="S3" s="3"/>
     </row>
     <row r="4" spans="1:19" ht="4.95" customHeight="1">
       <c r="A4" s="2"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="31"/>
-      <c r="I4" s="31"/>
-      <c r="J4" s="31"/>
-      <c r="K4" s="31"/>
-      <c r="L4" s="31"/>
-      <c r="M4" s="31"/>
-      <c r="N4" s="31"/>
-      <c r="O4" s="25"/>
-      <c r="P4" s="31"/>
-      <c r="Q4" s="31"/>
-      <c r="R4" s="34"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="29"/>
+      <c r="L4" s="29"/>
+      <c r="M4" s="29"/>
+      <c r="N4" s="29"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="29"/>
+      <c r="Q4" s="29"/>
+      <c r="R4" s="31"/>
       <c r="S4" s="3"/>
     </row>
     <row r="5" spans="1:19" ht="4.2" customHeight="1">
@@ -1104,7 +1089,7 @@
       <c r="L5" s="6"/>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
-      <c r="O5" s="29"/>
+      <c r="O5" s="27"/>
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="13"/>
@@ -1113,35 +1098,35 @@
     <row r="6" spans="1:19">
       <c r="A6" s="2"/>
       <c r="B6" s="7"/>
-      <c r="C6" s="36" t="s">
+      <c r="C6" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="27"/>
-      <c r="E6" s="26" t="s">
+      <c r="D6" s="25"/>
+      <c r="E6" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="26"/>
-      <c r="J6" s="26"/>
-      <c r="K6" s="60"/>
-      <c r="L6" s="59"/>
-      <c r="M6" s="59"/>
-      <c r="N6" s="59"/>
-      <c r="O6" s="59" t="s">
+      <c r="F6" s="51"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="51"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="14"/>
+      <c r="N6" s="14"/>
+      <c r="O6" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="P6" s="59"/>
-      <c r="Q6" s="59"/>
-      <c r="R6" s="60"/>
+      <c r="P6" s="14"/>
+      <c r="Q6" s="14"/>
+      <c r="R6" s="15"/>
       <c r="S6" s="3"/>
     </row>
     <row r="7" spans="1:19">
       <c r="A7" s="2"/>
       <c r="B7" s="7"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="27"/>
+      <c r="C7" s="50"/>
+      <c r="D7" s="25"/>
       <c r="E7" s="14" t="s">
         <v>9</v>
       </c>
@@ -1172,7 +1157,7 @@
       <c r="N7" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="O7" s="28" t="s">
+      <c r="O7" s="26" t="s">
         <v>19</v>
       </c>
       <c r="P7" s="14" t="s">
@@ -1201,7 +1186,7 @@
       <c r="L8" s="12"/>
       <c r="M8" s="12"/>
       <c r="N8" s="12"/>
-      <c r="O8" s="25"/>
+      <c r="O8" s="2"/>
       <c r="P8" s="12"/>
       <c r="Q8" s="12"/>
       <c r="R8" s="16"/>
@@ -1210,7 +1195,7 @@
     <row r="9" spans="1:19" ht="12" customHeight="1">
       <c r="A9" s="2"/>
       <c r="B9" s="8"/>
-      <c r="C9" s="37" t="s">
+      <c r="C9" s="33" t="s">
         <v>0</v>
       </c>
       <c r="D9" s="17"/>
@@ -1224,7 +1209,7 @@
       <c r="L9" s="12"/>
       <c r="M9" s="12"/>
       <c r="N9" s="12"/>
-      <c r="O9" s="25"/>
+      <c r="O9" s="2"/>
       <c r="P9" s="12"/>
       <c r="Q9" s="12"/>
       <c r="R9" s="16"/>
@@ -1233,7 +1218,7 @@
     <row r="10" spans="1:19" ht="6" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="8"/>
-      <c r="C10" s="38"/>
+      <c r="C10" s="34"/>
       <c r="D10" s="17"/>
       <c r="E10" s="12"/>
       <c r="F10" s="12"/>
@@ -1245,7 +1230,7 @@
       <c r="L10" s="12"/>
       <c r="M10" s="12"/>
       <c r="N10" s="12"/>
-      <c r="O10" s="25"/>
+      <c r="O10" s="2"/>
       <c r="P10" s="12"/>
       <c r="Q10" s="12"/>
       <c r="R10" s="16"/>
@@ -1254,7 +1239,7 @@
     <row r="11" spans="1:19" ht="6" customHeight="1">
       <c r="A11" s="2"/>
       <c r="B11" s="8"/>
-      <c r="C11" s="39" t="s">
+      <c r="C11" s="52" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="18"/>
@@ -1268,7 +1253,7 @@
       <c r="L11" s="12"/>
       <c r="M11" s="12"/>
       <c r="N11" s="12"/>
-      <c r="O11" s="25"/>
+      <c r="O11" s="2"/>
       <c r="P11" s="12"/>
       <c r="Q11" s="12"/>
       <c r="R11" s="16"/>
@@ -1277,7 +1262,7 @@
     <row r="12" spans="1:19" ht="6" customHeight="1">
       <c r="A12" s="2"/>
       <c r="B12" s="8"/>
-      <c r="C12" s="39"/>
+      <c r="C12" s="52"/>
       <c r="D12" s="18"/>
       <c r="E12" s="20"/>
       <c r="F12" s="12"/>
@@ -1289,7 +1274,7 @@
       <c r="L12" s="12"/>
       <c r="M12" s="12"/>
       <c r="N12" s="12"/>
-      <c r="O12" s="25"/>
+      <c r="O12" s="2"/>
       <c r="P12" s="12"/>
       <c r="Q12" s="12"/>
       <c r="R12" s="16"/>
@@ -1298,7 +1283,7 @@
     <row r="13" spans="1:19" ht="6" customHeight="1">
       <c r="A13" s="2"/>
       <c r="B13" s="8"/>
-      <c r="C13" s="40"/>
+      <c r="C13" s="35"/>
       <c r="D13" s="18"/>
       <c r="E13" s="12"/>
       <c r="F13" s="12"/>
@@ -1310,7 +1295,7 @@
       <c r="L13" s="12"/>
       <c r="M13" s="12"/>
       <c r="N13" s="12"/>
-      <c r="O13" s="25"/>
+      <c r="O13" s="2"/>
       <c r="P13" s="12"/>
       <c r="Q13" s="12"/>
       <c r="R13" s="16"/>
@@ -1319,7 +1304,7 @@
     <row r="14" spans="1:19" ht="6" customHeight="1">
       <c r="A14" s="2"/>
       <c r="B14" s="8"/>
-      <c r="C14" s="41" t="s">
+      <c r="C14" s="49" t="s">
         <v>8</v>
       </c>
       <c r="D14" s="18"/>
@@ -1333,7 +1318,7 @@
       <c r="L14" s="12"/>
       <c r="M14" s="12"/>
       <c r="N14" s="12"/>
-      <c r="O14" s="25"/>
+      <c r="O14" s="2"/>
       <c r="P14" s="12"/>
       <c r="Q14" s="12"/>
       <c r="R14" s="16"/>
@@ -1342,19 +1327,19 @@
     <row r="15" spans="1:19" ht="6" customHeight="1">
       <c r="A15" s="2"/>
       <c r="B15" s="8"/>
-      <c r="C15" s="41"/>
+      <c r="C15" s="49"/>
       <c r="D15" s="18"/>
       <c r="E15" s="20"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
       <c r="I15" s="12"/>
       <c r="J15" s="12"/>
       <c r="K15" s="12"/>
       <c r="L15" s="12"/>
       <c r="M15" s="12"/>
       <c r="N15" s="12"/>
-      <c r="O15" s="25"/>
+      <c r="O15" s="2"/>
       <c r="P15" s="12"/>
       <c r="Q15" s="12"/>
       <c r="R15" s="16"/>
@@ -1363,7 +1348,7 @@
     <row r="16" spans="1:19" ht="6" customHeight="1">
       <c r="A16" s="2"/>
       <c r="B16" s="8"/>
-      <c r="C16" s="40"/>
+      <c r="C16" s="35"/>
       <c r="D16" s="18"/>
       <c r="E16" s="12"/>
       <c r="F16" s="12"/>
@@ -1375,7 +1360,7 @@
       <c r="L16" s="12"/>
       <c r="M16" s="12"/>
       <c r="N16" s="12"/>
-      <c r="O16" s="25"/>
+      <c r="O16" s="2"/>
       <c r="P16" s="12"/>
       <c r="Q16" s="12"/>
       <c r="R16" s="16"/>
@@ -1384,7 +1369,7 @@
     <row r="17" spans="1:25" ht="12" customHeight="1">
       <c r="A17" s="2"/>
       <c r="B17" s="8"/>
-      <c r="C17" s="42" t="s">
+      <c r="C17" s="36" t="s">
         <v>23</v>
       </c>
       <c r="D17" s="12"/>
@@ -1398,7 +1383,7 @@
       <c r="L17" s="12"/>
       <c r="M17" s="12"/>
       <c r="N17" s="12"/>
-      <c r="O17" s="25"/>
+      <c r="O17" s="2"/>
       <c r="P17" s="12"/>
       <c r="Q17" s="12"/>
       <c r="R17" s="16"/>
@@ -1407,8 +1392,8 @@
     <row r="18" spans="1:25" ht="6" customHeight="1">
       <c r="A18" s="2"/>
       <c r="B18" s="8"/>
-      <c r="C18" s="43" t="s">
-        <v>24</v>
+      <c r="C18" s="47" t="s">
+        <v>36</v>
       </c>
       <c r="D18" s="18"/>
       <c r="E18" s="12"/>
@@ -1420,7 +1405,7 @@
       <c r="L18" s="12"/>
       <c r="M18" s="12"/>
       <c r="N18" s="12"/>
-      <c r="O18" s="25"/>
+      <c r="O18" s="2"/>
       <c r="P18" s="12"/>
       <c r="Q18" s="12"/>
       <c r="R18" s="16"/>
@@ -1429,19 +1414,19 @@
     <row r="19" spans="1:25" ht="6" customHeight="1">
       <c r="A19" s="2"/>
       <c r="B19" s="8"/>
-      <c r="C19" s="43"/>
+      <c r="C19" s="47"/>
       <c r="D19" s="18"/>
       <c r="E19" s="12"/>
       <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12"/>
       <c r="L19" s="12"/>
       <c r="M19" s="12"/>
       <c r="N19" s="12"/>
-      <c r="O19" s="25"/>
+      <c r="O19" s="2"/>
       <c r="P19" s="12"/>
       <c r="Q19" s="12"/>
       <c r="R19" s="16"/>
@@ -1450,7 +1435,7 @@
     <row r="20" spans="1:25" ht="6" customHeight="1">
       <c r="A20" s="2"/>
       <c r="B20" s="8"/>
-      <c r="C20" s="40"/>
+      <c r="C20" s="35"/>
       <c r="D20" s="18"/>
       <c r="E20" s="12"/>
       <c r="F20" s="12"/>
@@ -1462,7 +1447,7 @@
       <c r="L20" s="12"/>
       <c r="M20" s="12"/>
       <c r="N20" s="12"/>
-      <c r="O20" s="25"/>
+      <c r="O20" s="2"/>
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
       <c r="R20" s="16"/>
@@ -1471,8 +1456,8 @@
     <row r="21" spans="1:25" ht="6" customHeight="1">
       <c r="A21" s="2"/>
       <c r="B21" s="8"/>
-      <c r="C21" s="43" t="s">
-        <v>31</v>
+      <c r="C21" s="47" t="s">
+        <v>28</v>
       </c>
       <c r="D21" s="18"/>
       <c r="E21" s="12"/>
@@ -1480,12 +1465,12 @@
       <c r="G21" s="12"/>
       <c r="H21" s="19"/>
       <c r="I21" s="19"/>
-      <c r="J21" s="25"/>
+      <c r="J21" s="2"/>
       <c r="K21" s="12"/>
       <c r="L21" s="12"/>
       <c r="M21" s="12"/>
       <c r="N21" s="12"/>
-      <c r="O21" s="25"/>
+      <c r="O21" s="2"/>
       <c r="P21" s="12"/>
       <c r="Q21" s="12"/>
       <c r="R21" s="16"/>
@@ -1494,19 +1479,19 @@
     <row r="22" spans="1:25" ht="6" customHeight="1">
       <c r="A22" s="2"/>
       <c r="B22" s="8"/>
-      <c r="C22" s="43"/>
+      <c r="C22" s="47"/>
       <c r="D22" s="18"/>
       <c r="E22" s="12"/>
       <c r="F22" s="12"/>
       <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="12"/>
-      <c r="J22" s="25"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="2"/>
       <c r="K22" s="12"/>
       <c r="L22" s="12"/>
       <c r="M22" s="12"/>
       <c r="N22" s="12"/>
-      <c r="O22" s="25"/>
+      <c r="O22" s="2"/>
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
       <c r="R22" s="16"/>
@@ -1515,19 +1500,19 @@
     <row r="23" spans="1:25" ht="6" customHeight="1">
       <c r="A23" s="2"/>
       <c r="B23" s="8"/>
-      <c r="C23" s="40"/>
+      <c r="C23" s="35"/>
       <c r="D23" s="18"/>
       <c r="E23" s="12"/>
       <c r="F23" s="12"/>
       <c r="G23" s="12"/>
       <c r="H23" s="12"/>
       <c r="I23" s="12"/>
-      <c r="J23" s="25"/>
+      <c r="J23" s="2"/>
       <c r="K23" s="12"/>
       <c r="L23" s="12"/>
       <c r="M23" s="12"/>
       <c r="N23" s="12"/>
-      <c r="O23" s="25"/>
+      <c r="O23" s="2"/>
       <c r="P23" s="12"/>
       <c r="Q23" s="12"/>
       <c r="R23" s="16"/>
@@ -1536,8 +1521,8 @@
     <row r="24" spans="1:25" ht="6" customHeight="1">
       <c r="A24" s="2"/>
       <c r="B24" s="8"/>
-      <c r="C24" s="43" t="s">
-        <v>32</v>
+      <c r="C24" s="47" t="s">
+        <v>29</v>
       </c>
       <c r="D24" s="18"/>
       <c r="E24" s="12"/>
@@ -1545,12 +1530,12 @@
       <c r="G24" s="12"/>
       <c r="H24" s="19"/>
       <c r="I24" s="19"/>
-      <c r="J24" s="25"/>
+      <c r="J24" s="2"/>
       <c r="K24" s="12"/>
       <c r="L24" s="12"/>
       <c r="M24" s="12"/>
       <c r="N24" s="12"/>
-      <c r="O24" s="25"/>
+      <c r="O24" s="2"/>
       <c r="P24" s="12"/>
       <c r="Q24" s="12"/>
       <c r="R24" s="16"/>
@@ -1559,19 +1544,19 @@
     <row r="25" spans="1:25" ht="6" customHeight="1">
       <c r="A25" s="2"/>
       <c r="B25" s="8"/>
-      <c r="C25" s="43"/>
+      <c r="C25" s="47"/>
       <c r="D25" s="18"/>
       <c r="E25" s="12"/>
       <c r="F25" s="12"/>
       <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="12"/>
-      <c r="J25" s="25"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="2"/>
       <c r="K25" s="12"/>
       <c r="L25" s="12"/>
       <c r="M25" s="12"/>
       <c r="N25" s="22"/>
-      <c r="O25" s="25"/>
+      <c r="O25" s="2"/>
       <c r="P25" s="22"/>
       <c r="Q25" s="22"/>
       <c r="R25" s="23"/>
@@ -1580,19 +1565,19 @@
     <row r="26" spans="1:25" ht="6" customHeight="1">
       <c r="A26" s="2"/>
       <c r="B26" s="8"/>
-      <c r="C26" s="40"/>
+      <c r="C26" s="35"/>
       <c r="D26" s="18"/>
       <c r="E26" s="12"/>
       <c r="F26" s="12"/>
       <c r="G26" s="12"/>
       <c r="H26" s="12"/>
       <c r="I26" s="12"/>
-      <c r="J26" s="25"/>
+      <c r="J26" s="2"/>
       <c r="K26" s="12"/>
       <c r="L26" s="12"/>
       <c r="M26" s="12"/>
       <c r="N26" s="12"/>
-      <c r="O26" s="25"/>
+      <c r="O26" s="2"/>
       <c r="P26" s="12"/>
       <c r="Q26" s="12"/>
       <c r="R26" s="16"/>
@@ -1601,8 +1586,8 @@
     <row r="27" spans="1:25" ht="6" customHeight="1">
       <c r="A27" s="2"/>
       <c r="B27" s="8"/>
-      <c r="C27" s="43" t="s">
-        <v>35</v>
+      <c r="C27" s="47" t="s">
+        <v>32</v>
       </c>
       <c r="D27" s="18"/>
       <c r="E27" s="12"/>
@@ -1610,12 +1595,12 @@
       <c r="G27" s="12"/>
       <c r="H27" s="19"/>
       <c r="I27" s="19"/>
-      <c r="J27" s="25"/>
+      <c r="J27" s="2"/>
       <c r="K27" s="12"/>
       <c r="L27" s="12"/>
       <c r="M27" s="12"/>
       <c r="N27" s="12"/>
-      <c r="O27" s="25"/>
+      <c r="O27" s="2"/>
       <c r="P27" s="12"/>
       <c r="Q27" s="12"/>
       <c r="R27" s="16"/>
@@ -1624,19 +1609,19 @@
     <row r="28" spans="1:25" ht="6" customHeight="1">
       <c r="A28" s="2"/>
       <c r="B28" s="8"/>
-      <c r="C28" s="43"/>
+      <c r="C28" s="47"/>
       <c r="D28" s="18"/>
       <c r="E28" s="12"/>
       <c r="F28" s="12"/>
       <c r="G28" s="12"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="12"/>
-      <c r="J28" s="25"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="2"/>
       <c r="K28" s="12"/>
       <c r="L28" s="12"/>
       <c r="M28" s="12"/>
       <c r="N28" s="12"/>
-      <c r="O28" s="25"/>
+      <c r="O28" s="2"/>
       <c r="P28" s="12"/>
       <c r="Q28" s="12"/>
       <c r="R28" s="16"/>
@@ -1645,7 +1630,7 @@
     <row r="29" spans="1:25" ht="6" customHeight="1">
       <c r="A29" s="2"/>
       <c r="B29" s="8"/>
-      <c r="C29" s="40"/>
+      <c r="C29" s="35"/>
       <c r="D29" s="18"/>
       <c r="E29" s="12"/>
       <c r="F29" s="12"/>
@@ -1657,7 +1642,7 @@
       <c r="L29" s="12"/>
       <c r="M29" s="12"/>
       <c r="N29" s="12"/>
-      <c r="O29" s="25"/>
+      <c r="O29" s="2"/>
       <c r="P29" s="12"/>
       <c r="Q29" s="12"/>
       <c r="R29" s="16"/>
@@ -1666,8 +1651,8 @@
     <row r="30" spans="1:25" ht="12" customHeight="1">
       <c r="A30" s="2"/>
       <c r="B30" s="8"/>
-      <c r="C30" s="42" t="s">
-        <v>25</v>
+      <c r="C30" s="36" t="s">
+        <v>24</v>
       </c>
       <c r="D30" s="12"/>
       <c r="E30" s="12"/>
@@ -1680,7 +1665,7 @@
       <c r="L30" s="12"/>
       <c r="M30" s="12"/>
       <c r="N30" s="12"/>
-      <c r="O30" s="25"/>
+      <c r="O30" s="2"/>
       <c r="P30" s="12"/>
       <c r="Q30" s="12"/>
       <c r="R30" s="16"/>
@@ -1690,21 +1675,21 @@
     <row r="31" spans="1:25" ht="6" customHeight="1">
       <c r="A31" s="2"/>
       <c r="B31" s="8"/>
-      <c r="C31" s="44" t="s">
-        <v>26</v>
+      <c r="C31" s="48" t="s">
+        <v>34</v>
       </c>
       <c r="D31" s="18"/>
       <c r="E31" s="12"/>
-      <c r="F31" s="25"/>
-      <c r="G31" s="25"/>
-      <c r="H31" s="25"/>
-      <c r="I31" s="25"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
       <c r="J31" s="19"/>
       <c r="K31" s="19"/>
       <c r="L31" s="19"/>
       <c r="M31" s="19"/>
       <c r="N31" s="12"/>
-      <c r="O31" s="25"/>
+      <c r="O31" s="2"/>
       <c r="P31" s="12"/>
       <c r="Q31" s="12"/>
       <c r="R31" s="16"/>
@@ -1713,19 +1698,19 @@
     <row r="32" spans="1:25" ht="6" customHeight="1">
       <c r="A32" s="2"/>
       <c r="B32" s="8"/>
-      <c r="C32" s="44"/>
+      <c r="C32" s="48"/>
       <c r="D32" s="18"/>
       <c r="E32" s="12"/>
-      <c r="F32" s="25"/>
-      <c r="G32" s="25"/>
-      <c r="H32" s="25"/>
-      <c r="I32" s="25"/>
-      <c r="J32" s="12"/>
-      <c r="K32" s="12"/>
-      <c r="L32" s="12"/>
-      <c r="M32" s="12"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="20"/>
+      <c r="K32" s="20"/>
+      <c r="L32" s="20"/>
+      <c r="M32" s="20"/>
       <c r="N32" s="12"/>
-      <c r="O32" s="25"/>
+      <c r="O32" s="2"/>
       <c r="P32" s="12"/>
       <c r="Q32" s="12"/>
       <c r="R32" s="16"/>
@@ -1734,7 +1719,7 @@
     <row r="33" spans="1:19" ht="6" customHeight="1">
       <c r="A33" s="2"/>
       <c r="B33" s="8"/>
-      <c r="C33" s="40"/>
+      <c r="C33" s="35"/>
       <c r="D33" s="18"/>
       <c r="E33" s="12"/>
       <c r="F33" s="12"/>
@@ -1746,7 +1731,7 @@
       <c r="L33" s="12"/>
       <c r="M33" s="12"/>
       <c r="N33" s="12"/>
-      <c r="O33" s="25"/>
+      <c r="O33" s="2"/>
       <c r="P33" s="12"/>
       <c r="Q33" s="12"/>
       <c r="R33" s="16"/>
@@ -1755,8 +1740,8 @@
     <row r="34" spans="1:19" ht="6" customHeight="1">
       <c r="A34" s="2"/>
       <c r="B34" s="8"/>
-      <c r="C34" s="44" t="s">
-        <v>27</v>
+      <c r="C34" s="48" t="s">
+        <v>35</v>
       </c>
       <c r="D34" s="18"/>
       <c r="E34" s="12"/>
@@ -1768,8 +1753,8 @@
       <c r="K34" s="19"/>
       <c r="L34" s="19"/>
       <c r="M34" s="19"/>
-      <c r="N34" s="25"/>
-      <c r="O34" s="25"/>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
       <c r="P34" s="12"/>
       <c r="Q34" s="12"/>
       <c r="R34" s="16"/>
@@ -1778,19 +1763,19 @@
     <row r="35" spans="1:19" ht="6" customHeight="1">
       <c r="A35" s="2"/>
       <c r="B35" s="8"/>
-      <c r="C35" s="44"/>
+      <c r="C35" s="48"/>
       <c r="D35" s="18"/>
       <c r="E35" s="12"/>
       <c r="F35" s="12"/>
       <c r="G35" s="12"/>
       <c r="H35" s="12"/>
       <c r="I35" s="12"/>
-      <c r="J35" s="12"/>
-      <c r="K35" s="12"/>
-      <c r="L35" s="12"/>
-      <c r="M35" s="12"/>
-      <c r="N35" s="25"/>
-      <c r="O35" s="25"/>
+      <c r="J35" s="20"/>
+      <c r="K35" s="20"/>
+      <c r="L35" s="20"/>
+      <c r="M35" s="20"/>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
       <c r="P35" s="12"/>
       <c r="Q35" s="12"/>
       <c r="R35" s="16"/>
@@ -1799,7 +1784,7 @@
     <row r="36" spans="1:19" ht="6" customHeight="1">
       <c r="A36" s="2"/>
       <c r="B36" s="8"/>
-      <c r="C36" s="40"/>
+      <c r="C36" s="35"/>
       <c r="D36" s="18"/>
       <c r="E36" s="12"/>
       <c r="F36" s="12"/>
@@ -1811,7 +1796,7 @@
       <c r="L36" s="12"/>
       <c r="M36" s="12"/>
       <c r="N36" s="12"/>
-      <c r="O36" s="25"/>
+      <c r="O36" s="2"/>
       <c r="P36" s="12"/>
       <c r="Q36" s="12"/>
       <c r="R36" s="16"/>
@@ -1820,21 +1805,21 @@
     <row r="37" spans="1:19" ht="6" customHeight="1">
       <c r="A37" s="2"/>
       <c r="B37" s="8"/>
-      <c r="C37" s="44" t="s">
-        <v>33</v>
+      <c r="C37" s="48" t="s">
+        <v>30</v>
       </c>
       <c r="D37" s="18"/>
       <c r="E37" s="12"/>
-      <c r="F37" s="25"/>
-      <c r="G37" s="25"/>
-      <c r="H37" s="25"/>
-      <c r="I37" s="25"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
       <c r="J37" s="19"/>
       <c r="K37" s="19"/>
       <c r="L37" s="19"/>
       <c r="M37" s="19"/>
       <c r="N37" s="12"/>
-      <c r="O37" s="25"/>
+      <c r="O37" s="2"/>
       <c r="P37" s="12"/>
       <c r="Q37" s="12"/>
       <c r="R37" s="16"/>
@@ -1843,19 +1828,19 @@
     <row r="38" spans="1:19" ht="6" customHeight="1">
       <c r="A38" s="2"/>
       <c r="B38" s="8"/>
-      <c r="C38" s="44"/>
+      <c r="C38" s="48"/>
       <c r="D38" s="18"/>
       <c r="E38" s="12"/>
-      <c r="F38" s="25"/>
-      <c r="G38" s="25"/>
-      <c r="H38" s="25"/>
-      <c r="I38" s="25"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
       <c r="J38" s="12"/>
       <c r="K38" s="12"/>
       <c r="L38" s="12"/>
-      <c r="M38" s="12"/>
-      <c r="N38" s="12"/>
-      <c r="O38" s="25"/>
+      <c r="M38" s="20"/>
+      <c r="N38" s="20"/>
+      <c r="O38" s="2"/>
       <c r="P38" s="12"/>
       <c r="Q38" s="12"/>
       <c r="R38" s="16"/>
@@ -1864,8 +1849,8 @@
     <row r="39" spans="1:19" ht="12" customHeight="1">
       <c r="A39" s="2"/>
       <c r="B39" s="8"/>
-      <c r="C39" s="42" t="s">
-        <v>28</v>
+      <c r="C39" s="36" t="s">
+        <v>25</v>
       </c>
       <c r="D39" s="12"/>
       <c r="E39" s="12"/>
@@ -1878,7 +1863,7 @@
       <c r="L39" s="12"/>
       <c r="M39" s="12"/>
       <c r="N39" s="12"/>
-      <c r="O39" s="25"/>
+      <c r="O39" s="2"/>
       <c r="P39" s="12"/>
       <c r="Q39" s="12"/>
       <c r="R39" s="16"/>
@@ -1888,22 +1873,20 @@
       <c r="A40" s="2"/>
       <c r="B40" s="8"/>
       <c r="C40" s="45" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D40" s="18"/>
       <c r="E40" s="12"/>
       <c r="F40" s="12"/>
-      <c r="G40" s="33"/>
-      <c r="H40" s="33"/>
       <c r="I40" s="12"/>
       <c r="J40" s="12"/>
-      <c r="K40" s="25"/>
-      <c r="L40" s="25"/>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2"/>
       <c r="M40" s="19"/>
       <c r="N40" s="19"/>
       <c r="O40" s="19"/>
-      <c r="P40" s="25"/>
-      <c r="Q40" s="25"/>
+      <c r="P40" s="2"/>
+      <c r="Q40" s="2"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
     </row>
@@ -1912,26 +1895,26 @@
       <c r="B41" s="8"/>
       <c r="C41" s="45"/>
       <c r="D41" s="18"/>
-      <c r="E41" s="25"/>
-      <c r="F41" s="25"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
       <c r="G41" s="12"/>
       <c r="H41" s="12"/>
       <c r="I41" s="12"/>
       <c r="J41" s="12"/>
-      <c r="K41" s="25"/>
-      <c r="L41" s="25"/>
-      <c r="M41" s="25"/>
-      <c r="N41" s="25"/>
-      <c r="O41" s="25"/>
-      <c r="P41" s="25"/>
-      <c r="Q41" s="25"/>
+      <c r="K41" s="2"/>
+      <c r="L41" s="2"/>
+      <c r="M41" s="20"/>
+      <c r="N41" s="20"/>
+      <c r="O41" s="2"/>
+      <c r="P41" s="2"/>
+      <c r="Q41" s="2"/>
       <c r="R41" s="3"/>
       <c r="S41" s="3"/>
     </row>
     <row r="42" spans="1:19" ht="6" customHeight="1">
       <c r="A42" s="2"/>
       <c r="B42" s="8"/>
-      <c r="C42" s="40"/>
+      <c r="C42" s="35"/>
       <c r="D42" s="18"/>
       <c r="E42" s="12"/>
       <c r="F42" s="12"/>
@@ -1943,7 +1926,7 @@
       <c r="L42" s="12"/>
       <c r="M42" s="12"/>
       <c r="N42" s="12"/>
-      <c r="O42" s="25"/>
+      <c r="O42" s="2"/>
       <c r="P42" s="12"/>
       <c r="Q42" s="12"/>
       <c r="R42" s="16"/>
@@ -1953,7 +1936,7 @@
       <c r="A43" s="2"/>
       <c r="B43" s="8"/>
       <c r="C43" s="45" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="12"/>
@@ -1968,7 +1951,7 @@
       <c r="N43" s="19"/>
       <c r="O43" s="19"/>
       <c r="P43" s="12"/>
-      <c r="Q43" s="25"/>
+      <c r="Q43" s="2"/>
       <c r="R43" s="3"/>
       <c r="S43" s="3"/>
     </row>
@@ -1986,17 +1969,17 @@
       <c r="K44" s="12"/>
       <c r="L44" s="12"/>
       <c r="M44" s="12"/>
-      <c r="N44" s="12"/>
-      <c r="O44" s="25"/>
-      <c r="P44" s="12"/>
-      <c r="Q44" s="12"/>
+      <c r="N44" s="20"/>
+      <c r="O44" s="20"/>
+      <c r="P44" s="20"/>
+      <c r="Q44" s="20"/>
       <c r="R44" s="16"/>
       <c r="S44" s="3"/>
     </row>
     <row r="45" spans="1:19" ht="6" customHeight="1">
       <c r="A45" s="2"/>
       <c r="B45" s="8"/>
-      <c r="C45" s="40"/>
+      <c r="C45" s="35"/>
       <c r="D45" s="18"/>
       <c r="E45" s="12"/>
       <c r="F45" s="12"/>
@@ -2008,7 +1991,7 @@
       <c r="L45" s="12"/>
       <c r="M45" s="12"/>
       <c r="N45" s="12"/>
-      <c r="O45" s="25"/>
+      <c r="O45" s="2"/>
       <c r="P45" s="12"/>
       <c r="Q45" s="12"/>
       <c r="R45" s="16"/>
@@ -2018,7 +2001,7 @@
       <c r="A46" s="2"/>
       <c r="B46" s="8"/>
       <c r="C46" s="45" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D46" s="18"/>
       <c r="E46" s="12"/>
@@ -2051,17 +2034,17 @@
       <c r="K47" s="12"/>
       <c r="L47" s="12"/>
       <c r="M47" s="12"/>
-      <c r="N47" s="12"/>
-      <c r="O47" s="25"/>
-      <c r="P47" s="12"/>
-      <c r="Q47" s="12"/>
+      <c r="N47" s="20"/>
+      <c r="O47" s="20"/>
+      <c r="P47" s="20"/>
+      <c r="Q47" s="20"/>
       <c r="R47" s="16"/>
       <c r="S47" s="3"/>
     </row>
     <row r="48" spans="1:19" ht="6" customHeight="1">
       <c r="A48" s="2"/>
       <c r="B48" s="8"/>
-      <c r="C48" s="40"/>
+      <c r="C48" s="35"/>
       <c r="D48" s="18"/>
       <c r="E48" s="12"/>
       <c r="F48" s="12"/>
@@ -2073,7 +2056,7 @@
       <c r="L48" s="12"/>
       <c r="M48" s="12"/>
       <c r="N48" s="12"/>
-      <c r="O48" s="25"/>
+      <c r="O48" s="2"/>
       <c r="P48" s="12"/>
       <c r="Q48" s="12"/>
       <c r="R48" s="16"/>
@@ -2096,7 +2079,7 @@
       <c r="L49" s="12"/>
       <c r="M49" s="12"/>
       <c r="N49" s="12"/>
-      <c r="O49" s="25"/>
+      <c r="O49" s="2"/>
       <c r="P49" s="19"/>
       <c r="Q49" s="19"/>
       <c r="R49" s="24"/>
@@ -2117,10 +2100,10 @@
       <c r="L50" s="12"/>
       <c r="M50" s="12"/>
       <c r="N50" s="12"/>
-      <c r="O50" s="25"/>
+      <c r="O50" s="2"/>
       <c r="P50" s="12"/>
-      <c r="Q50" s="12"/>
-      <c r="R50" s="16"/>
+      <c r="Q50" s="20"/>
+      <c r="R50" s="20"/>
       <c r="S50" s="3"/>
     </row>
     <row r="51" spans="1:19" ht="6" customHeight="1">
@@ -2138,7 +2121,7 @@
       <c r="L51" s="10"/>
       <c r="M51" s="10"/>
       <c r="N51" s="10"/>
-      <c r="O51" s="30"/>
+      <c r="O51" s="28"/>
       <c r="P51" s="10"/>
       <c r="Q51" s="10"/>
       <c r="R51" s="21"/>
@@ -2147,22 +2130,22 @@
     <row r="52" spans="1:19" ht="6" customHeight="1">
       <c r="A52" s="2"/>
       <c r="B52" s="8"/>
-      <c r="C52" s="51"/>
-      <c r="D52" s="52"/>
-      <c r="E52" s="52"/>
-      <c r="F52" s="52"/>
-      <c r="G52" s="52"/>
-      <c r="H52" s="52"/>
-      <c r="I52" s="52"/>
-      <c r="J52" s="52"/>
-      <c r="K52" s="52"/>
-      <c r="L52" s="52"/>
-      <c r="M52" s="52"/>
-      <c r="N52" s="52"/>
-      <c r="O52" s="53"/>
-      <c r="P52" s="52"/>
-      <c r="Q52" s="52"/>
-      <c r="R52" s="54"/>
+      <c r="C52" s="40"/>
+      <c r="D52" s="41"/>
+      <c r="E52" s="41"/>
+      <c r="F52" s="41"/>
+      <c r="G52" s="41"/>
+      <c r="H52" s="41"/>
+      <c r="I52" s="41"/>
+      <c r="J52" s="41"/>
+      <c r="K52" s="41"/>
+      <c r="L52" s="41"/>
+      <c r="M52" s="41"/>
+      <c r="N52" s="41"/>
+      <c r="O52" s="42"/>
+      <c r="P52" s="41"/>
+      <c r="Q52" s="41"/>
+      <c r="R52" s="43"/>
       <c r="S52" s="3"/>
     </row>
     <row r="53" spans="1:19" ht="6" customHeight="1">
@@ -2171,124 +2154,127 @@
       <c r="C53" s="8"/>
       <c r="D53" s="12"/>
       <c r="E53" s="12"/>
-      <c r="F53" s="32"/>
-      <c r="G53" s="32"/>
-      <c r="H53" s="32"/>
+      <c r="F53" s="30"/>
+      <c r="G53" s="30"/>
+      <c r="H53" s="30"/>
       <c r="I53" s="12"/>
       <c r="J53" s="12"/>
       <c r="K53" s="12"/>
-      <c r="L53" s="25"/>
-      <c r="M53" s="25"/>
-      <c r="N53" s="25"/>
+      <c r="L53" s="2"/>
+      <c r="M53" s="2"/>
+      <c r="N53" s="2"/>
       <c r="O53" s="19" t="s">
         <v>7</v>
       </c>
       <c r="P53" s="19"/>
-      <c r="Q53" s="47" t="s">
+      <c r="Q53" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="R53" s="35"/>
+      <c r="R53" s="32"/>
       <c r="S53" s="3"/>
     </row>
     <row r="54" spans="1:19" ht="6" customHeight="1">
       <c r="A54" s="2"/>
       <c r="B54" s="8"/>
-      <c r="C54" s="48"/>
-      <c r="D54" s="30"/>
-      <c r="E54" s="30"/>
-      <c r="F54" s="30"/>
-      <c r="G54" s="30"/>
-      <c r="H54" s="30"/>
-      <c r="I54" s="30"/>
-      <c r="J54" s="30"/>
-      <c r="K54" s="30"/>
-      <c r="L54" s="30"/>
-      <c r="M54" s="30"/>
-      <c r="N54" s="30"/>
-      <c r="O54" s="30"/>
-      <c r="P54" s="30"/>
-      <c r="Q54" s="30"/>
+      <c r="C54" s="38"/>
+      <c r="D54" s="28"/>
+      <c r="E54" s="28"/>
+      <c r="F54" s="28"/>
+      <c r="G54" s="28"/>
+      <c r="H54" s="28"/>
+      <c r="I54" s="28"/>
+      <c r="J54" s="28"/>
+      <c r="K54" s="28"/>
+      <c r="L54" s="28"/>
+      <c r="M54" s="28"/>
+      <c r="N54" s="28"/>
+      <c r="O54" s="28"/>
+      <c r="P54" s="28"/>
+      <c r="Q54" s="28"/>
       <c r="R54" s="4"/>
       <c r="S54" s="3"/>
     </row>
     <row r="55" spans="1:19" ht="6.6" customHeight="1">
       <c r="A55" s="2"/>
       <c r="B55" s="8"/>
-      <c r="C55" s="25"/>
-      <c r="D55" s="25"/>
-      <c r="E55" s="25"/>
-      <c r="F55" s="25"/>
-      <c r="G55" s="25"/>
-      <c r="H55" s="25"/>
-      <c r="I55" s="25"/>
-      <c r="J55" s="25"/>
-      <c r="K55" s="25"/>
-      <c r="L55" s="25"/>
-      <c r="M55" s="25"/>
-      <c r="N55" s="25"/>
-      <c r="O55" s="25"/>
-      <c r="P55" s="25"/>
-      <c r="Q55" s="25"/>
-      <c r="R55" s="25"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
+      <c r="I55" s="2"/>
+      <c r="J55" s="2"/>
+      <c r="K55" s="2"/>
+      <c r="L55" s="2"/>
+      <c r="M55" s="2"/>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
+      <c r="P55" s="2"/>
+      <c r="Q55" s="2"/>
+      <c r="R55" s="2"/>
       <c r="S55" s="3"/>
     </row>
     <row r="56" spans="1:19" ht="6.6" customHeight="1">
       <c r="A56" s="2"/>
       <c r="B56" s="8"/>
-      <c r="C56" s="25"/>
-      <c r="D56" s="25"/>
-      <c r="E56" s="25"/>
-      <c r="F56" s="25"/>
-      <c r="G56" s="25"/>
-      <c r="H56" s="25"/>
-      <c r="I56" s="25"/>
-      <c r="J56" s="25"/>
-      <c r="K56" s="25"/>
-      <c r="L56" s="25"/>
-      <c r="M56" s="25"/>
-      <c r="N56" s="25"/>
-      <c r="O56" s="25"/>
-      <c r="P56" s="25"/>
-      <c r="Q56" s="25"/>
-      <c r="R56" s="25"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+      <c r="I56" s="2"/>
+      <c r="J56" s="2"/>
+      <c r="K56" s="2"/>
+      <c r="L56" s="2"/>
+      <c r="M56" s="2"/>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
+      <c r="P56" s="2"/>
+      <c r="Q56" s="2"/>
+      <c r="R56" s="2"/>
       <c r="S56" s="3"/>
     </row>
     <row r="57" spans="1:19" ht="3" customHeight="1">
-      <c r="A57" s="25"/>
-      <c r="B57" s="48"/>
-      <c r="C57" s="30"/>
-      <c r="D57" s="30"/>
-      <c r="E57" s="30"/>
-      <c r="F57" s="30"/>
-      <c r="G57" s="30"/>
-      <c r="H57" s="30"/>
-      <c r="I57" s="30"/>
-      <c r="J57" s="30"/>
-      <c r="K57" s="30"/>
-      <c r="L57" s="30"/>
-      <c r="M57" s="30"/>
-      <c r="N57" s="30"/>
-      <c r="O57" s="30"/>
-      <c r="P57" s="30"/>
-      <c r="Q57" s="30"/>
-      <c r="R57" s="30"/>
+      <c r="A57" s="2"/>
+      <c r="B57" s="38"/>
+      <c r="C57" s="28"/>
+      <c r="D57" s="28"/>
+      <c r="E57" s="28"/>
+      <c r="F57" s="28"/>
+      <c r="G57" s="28"/>
+      <c r="H57" s="28"/>
+      <c r="I57" s="28"/>
+      <c r="J57" s="28"/>
+      <c r="K57" s="28"/>
+      <c r="L57" s="28"/>
+      <c r="M57" s="28"/>
+      <c r="N57" s="28"/>
+      <c r="O57" s="28"/>
+      <c r="P57" s="28"/>
+      <c r="Q57" s="28"/>
+      <c r="R57" s="28"/>
       <c r="S57" s="4"/>
     </row>
     <row r="58" spans="1:19" ht="6" customHeight="1">
-      <c r="A58" s="25"/>
+      <c r="A58" s="2"/>
       <c r="B58" s="12"/>
-      <c r="C58" s="33"/>
     </row>
     <row r="59" spans="1:19" ht="9" customHeight="1">
-      <c r="A59" s="25"/>
+      <c r="A59" s="2"/>
       <c r="B59" s="12"/>
-      <c r="C59" s="33"/>
     </row>
     <row r="60" spans="1:19">
       <c r="A60" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="E6:J6"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="B2:R3"/>
     <mergeCell ref="C43:C44"/>
     <mergeCell ref="C46:C47"/>
     <mergeCell ref="C49:C50"/>
@@ -2300,11 +2286,6 @@
     <mergeCell ref="C31:C32"/>
     <mergeCell ref="C34:C35"/>
     <mergeCell ref="C37:C38"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="E6:J6"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="B2:R3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
